--- a/astro-site/public/dl/restaurant-financial-plan-templates/03-restaurant-cash-flow-forecast.xlsx
+++ b/astro-site/public/dl/restaurant-financial-plan-templates/03-restaurant-cash-flow-forecast.xlsx
@@ -189,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -265,6 +265,9 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -861,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B25"/>
+  <dimension ref="A2:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -980,6 +983,13 @@
       <c r="B25" s="19" t="inlineStr">
         <is>
           <t>Version 2.0 · October 2026 · aichef.pro/en/digital-products/restaurant-financial-plan-templates · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="40" t="inlineStr">
+        <is>
+          <t>Planning tool, not financial, tax or legal advice. Requirements vary by state and city — check with your accountant and local authorities.</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1062,7 @@
       <c r="C4" s="23" t="n">
         <v>0.8</v>
       </c>
-      <c r="D4" s="40" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>Cash comes in the same day; cards arrive with a delay.</t>
         </is>
@@ -1067,7 +1077,7 @@
       <c r="C5" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="40" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>How long your POS and card processor take to deposit the money. Typical: D+1 or D+2.</t>
         </is>
@@ -1082,13 +1092,13 @@
       <c r="C6" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="D6" s="40" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr">
         <is>
           <t>Whatever you have negotiated. 0 = pay on delivery.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="24.5" customHeight="1">
+    <row r="7" ht="61.25" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
           <t>Sales tax / VAT charged on sales (%)</t>
@@ -1097,9 +1107,9 @@
       <c r="C7" s="26" t="n">
         <v>0.08</v>
       </c>
-      <c r="D7" s="40" t="inlineStr">
-        <is>
-          <t>US: your combined state + local rate on meals (8% is the kit's example). UK: 20% VAT.</t>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>US: your combined state + local rate on meals (8% is the kit's example). UK: 20% VAT. The tax row uses dine-in, bar and events (rows 7, 8 and 10): third-party delivery marketplaces usually collect and remit the sales tax on their orders in most US states; owner capital, loans and refunds are not taxable sales.</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1122,7 @@
       <c r="C8" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="40" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>US: 0 (sales tax has no input credit; buy food for resale with a resale certificate). UK: most food is 0%.</t>
         </is>
@@ -1127,7 +1137,7 @@
       <c r="C9" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="D9" s="41" t="inlineStr">
         <is>
           <t>US: 0. UK (VAT-registered): 20% on most expenses; on rent only if the landlord opted to tax.</t>
         </is>
@@ -1166,7 +1176,7 @@
       <c r="C13" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="42">
         <f>$C$26*$C13</f>
         <v>0.0</v>
       </c>
@@ -1180,7 +1190,7 @@
       <c r="C14" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="42">
         <f>$C$26*$C14</f>
         <v>0.0</v>
       </c>
@@ -1194,7 +1204,7 @@
       <c r="C15" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="42">
         <f>$C$26*$C15</f>
         <v>0.0</v>
       </c>
@@ -1208,7 +1218,7 @@
       <c r="C16" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="42">
         <f>$C$26*$C16</f>
         <v>0.0</v>
       </c>
@@ -1222,7 +1232,7 @@
       <c r="C17" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="42">
         <f>$C$26*$C17</f>
         <v>0.0</v>
       </c>
@@ -1236,7 +1246,7 @@
       <c r="C18" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="42">
         <f>$C$26*$C18</f>
         <v>0.0</v>
       </c>
@@ -1250,7 +1260,7 @@
       <c r="C19" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="42">
         <f>$C$26*$C19</f>
         <v>0.0</v>
       </c>
@@ -1264,7 +1274,7 @@
       <c r="C20" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="41">
+      <c r="D20" s="42">
         <f>$C$26*$C20</f>
         <v>0.0</v>
       </c>
@@ -1278,7 +1288,7 @@
       <c r="C21" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="41">
+      <c r="D21" s="42">
         <f>$C$26*$C21</f>
         <v>0.0</v>
       </c>
@@ -1292,7 +1302,7 @@
       <c r="C22" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="42">
         <f>$C$26*$C22</f>
         <v>0.0</v>
       </c>
@@ -1306,7 +1316,7 @@
       <c r="C23" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="42">
         <f>$C$26*$C23</f>
         <v>0.0</v>
       </c>
@@ -1320,7 +1330,7 @@
       <c r="C24" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="41">
+      <c r="D24" s="42">
         <f>$C$26*$C24</f>
         <v>0.0</v>
       </c>
@@ -1331,7 +1341,7 @@
           <t>Sales in a typical month (incl. sales tax)</t>
         </is>
       </c>
-      <c r="C26" s="42" t="n">
+      <c r="C26" s="43" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="24" t="inlineStr">
@@ -1356,13 +1366,17 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <dataValidations count="2">
-    <dataValidation sqref="C5 C6 C26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid amount" error="Enter a number greater than or equal to 0." type="decimal" operator="greaterThanOrEqual">
+  <dataValidations count="3">
+    <dataValidation sqref="C5 C26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid amount" error="Enter a number greater than or equal to 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="C4 C7 C8 C9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid percentage" error="Enter a percentage between 0 and 1 (0.35 = 35%)." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid payment terms" error="Enter 0 to 30 days. This sheet pays each month's purchases this month or next, so longer terms count as 30." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>30</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1497,50 +1511,50 @@
           <t>OPENING BALANCE</t>
         </is>
       </c>
-      <c r="B5" s="43" t="n">
+      <c r="B5" s="44" t="n">
         <v>15000</v>
       </c>
-      <c r="C5" s="44">
+      <c r="C5" s="45">
         <f>B29</f>
         <v>15000.0</v>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="45">
         <f>C29</f>
         <v>15000.0</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="45">
         <f>D29</f>
         <v>15000.0</v>
       </c>
-      <c r="F5" s="44">
+      <c r="F5" s="45">
         <f>E29</f>
         <v>15000.0</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="45">
         <f>F29</f>
         <v>15000.0</v>
       </c>
-      <c r="H5" s="44">
+      <c r="H5" s="45">
         <f>G29</f>
         <v>15000.0</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="45">
         <f>H29</f>
         <v>15000.0</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="45">
         <f>I29</f>
         <v>15000.0</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="45">
         <f>J29</f>
         <v>15000.0</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="45">
         <f>K29</f>
         <v>15000.0</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="45">
         <f>L29</f>
         <v>15000.0</v>
       </c>
@@ -1558,40 +1572,40 @@
           <t>Dine-in sales (incl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="43" t="n">
+      <c r="B7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1601,40 +1615,40 @@
           <t>Bar sales (incl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="43" t="n">
+      <c r="B8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1644,40 +1658,40 @@
           <t>Delivery sales (incl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="43" t="n">
+      <c r="B9" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1687,40 +1701,40 @@
           <t>Events / Catering (incl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="43" t="n">
+      <c r="B10" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1730,40 +1744,40 @@
           <t>Other receipts</t>
         </is>
       </c>
-      <c r="B11" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="43" t="n">
+      <c r="B11" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1773,51 +1787,51 @@
           <t>SALES FOR THE MONTH</t>
         </is>
       </c>
-      <c r="B12" s="44">
+      <c r="B12" s="45">
         <f>SUM(B7:B11)</f>
         <v>0.0</v>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="45">
         <f>SUM(C7:C11)</f>
         <v>0.0</v>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="45">
         <f>SUM(D7:D11)</f>
         <v>0.0</v>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="45">
         <f>SUM(E7:E11)</f>
         <v>0.0</v>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="45">
         <f>SUM(F7:F11)</f>
         <v>0.0</v>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="45">
         <f>SUM(G7:G11)</f>
         <v>0.0</v>
       </c>
-      <c r="H12" s="44">
+      <c r="H12" s="45">
         <f>SUM(H7:H11)</f>
         <v>0.0</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="45">
         <f>SUM(I7:I11)</f>
         <v>0.0</v>
       </c>
-      <c r="J12" s="44">
+      <c r="J12" s="45">
         <f>SUM(J7:J11)</f>
         <v>0.0</v>
       </c>
-      <c r="K12" s="44">
+      <c r="K12" s="45">
         <f>SUM(K7:K11)</f>
         <v>0.0</v>
       </c>
-      <c r="L12" s="44">
+      <c r="L12" s="45">
         <f>SUM(L7:L11)</f>
         <v>0.0</v>
       </c>
-      <c r="M12" s="44">
+      <c r="M12" s="45">
         <f>SUM(M7:M11)</f>
         <v>0.0</v>
       </c>
@@ -1828,51 +1842,51 @@
           <t>Card payouts pending (collected next month)</t>
         </is>
       </c>
-      <c r="B13" s="41">
+      <c r="B13" s="42">
         <f>IFERROR(B12*Assumptions!$C$4*Assumptions!$C$5/30,0)</f>
         <v>0.0</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="42">
         <f>IFERROR(C12*Assumptions!$C$4*Assumptions!$C$5/30,0)</f>
         <v>0.0</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="42">
         <f>IFERROR(D12*Assumptions!$C$4*Assumptions!$C$5/30,0)</f>
         <v>0.0</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="42">
         <f>IFERROR(E12*Assumptions!$C$4*Assumptions!$C$5/30,0)</f>
         <v>0.0</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="42">
         <f>IFERROR(F12*Assumptions!$C$4*Assumptions!$C$5/30,0)</f>
         <v>0.0</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="42">
         <f>IFERROR(G12*Assumptions!$C$4*Assumptions!$C$5/30,0)</f>
         <v>0.0</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="42">
         <f>IFERROR(H12*Assumptions!$C$4*Assumptions!$C$5/30,0)</f>
         <v>0.0</v>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="42">
         <f>IFERROR(I12*Assumptions!$C$4*Assumptions!$C$5/30,0)</f>
         <v>0.0</v>
       </c>
-      <c r="J13" s="41">
+      <c r="J13" s="42">
         <f>IFERROR(J12*Assumptions!$C$4*Assumptions!$C$5/30,0)</f>
         <v>0.0</v>
       </c>
-      <c r="K13" s="41">
+      <c r="K13" s="42">
         <f>IFERROR(K12*Assumptions!$C$4*Assumptions!$C$5/30,0)</f>
         <v>0.0</v>
       </c>
-      <c r="L13" s="41">
+      <c r="L13" s="42">
         <f>IFERROR(L12*Assumptions!$C$4*Assumptions!$C$5/30,0)</f>
         <v>0.0</v>
       </c>
-      <c r="M13" s="41">
+      <c r="M13" s="42">
         <f>IFERROR(M12*Assumptions!$C$4*Assumptions!$C$5/30,0)</f>
         <v>0.0</v>
       </c>
@@ -1883,51 +1897,51 @@
           <t>TOTAL CASH RECEIVED</t>
         </is>
       </c>
-      <c r="B14" s="44">
+      <c r="B14" s="45">
         <f>B12-B13</f>
         <v>0.0</v>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="45">
         <f>C12-C13+B13</f>
         <v>0.0</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="45">
         <f>D12-D13+C13</f>
         <v>0.0</v>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="45">
         <f>E12-E13+D13</f>
         <v>0.0</v>
       </c>
-      <c r="F14" s="44">
+      <c r="F14" s="45">
         <f>F12-F13+E13</f>
         <v>0.0</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="45">
         <f>G12-G13+F13</f>
         <v>0.0</v>
       </c>
-      <c r="H14" s="44">
+      <c r="H14" s="45">
         <f>H12-H13+G13</f>
         <v>0.0</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="45">
         <f>I12-I13+H13</f>
         <v>0.0</v>
       </c>
-      <c r="J14" s="44">
+      <c r="J14" s="45">
         <f>J12-J13+I13</f>
         <v>0.0</v>
       </c>
-      <c r="K14" s="44">
+      <c r="K14" s="45">
         <f>K12-K13+J13</f>
         <v>0.0</v>
       </c>
-      <c r="L14" s="44">
+      <c r="L14" s="45">
         <f>L12-L13+K13</f>
         <v>0.0</v>
       </c>
-      <c r="M14" s="44">
+      <c r="M14" s="45">
         <f>M12-M13+L13</f>
         <v>0.0</v>
       </c>
@@ -1957,52 +1971,52 @@
           <t>Supplier payments (per negotiated terms)</t>
         </is>
       </c>
-      <c r="B16" s="45">
-        <f>IFERROR(B33*(1-Assumptions!$C$6/30),0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="C16" s="45">
-        <f>IFERROR(C33*(1-Assumptions!$C$6/30)+B33*Assumptions!$C$6/30,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="D16" s="45">
-        <f>IFERROR(D33*(1-Assumptions!$C$6/30)+C33*Assumptions!$C$6/30,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E16" s="45">
-        <f>IFERROR(E33*(1-Assumptions!$C$6/30)+D33*Assumptions!$C$6/30,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="F16" s="45">
-        <f>IFERROR(F33*(1-Assumptions!$C$6/30)+E33*Assumptions!$C$6/30,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="G16" s="45">
-        <f>IFERROR(G33*(1-Assumptions!$C$6/30)+F33*Assumptions!$C$6/30,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="H16" s="45">
-        <f>IFERROR(H33*(1-Assumptions!$C$6/30)+G33*Assumptions!$C$6/30,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="45">
-        <f>IFERROR(I33*(1-Assumptions!$C$6/30)+H33*Assumptions!$C$6/30,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="J16" s="45">
-        <f>IFERROR(J33*(1-Assumptions!$C$6/30)+I33*Assumptions!$C$6/30,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="45">
-        <f>IFERROR(K33*(1-Assumptions!$C$6/30)+J33*Assumptions!$C$6/30,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="45">
-        <f>IFERROR(L33*(1-Assumptions!$C$6/30)+K33*Assumptions!$C$6/30,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="M16" s="45">
-        <f>IFERROR(M33*(1-Assumptions!$C$6/30)+L33*Assumptions!$C$6/30,0)</f>
+      <c r="B16" s="46">
+        <f>IFERROR(B33*(1-MIN(Assumptions!$C$6,30)/30),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C16" s="46">
+        <f>IFERROR(C33*(1-MIN(Assumptions!$C$6,30)/30)+B33*MIN(Assumptions!$C$6,30)/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D16" s="46">
+        <f>IFERROR(D33*(1-MIN(Assumptions!$C$6,30)/30)+C33*MIN(Assumptions!$C$6,30)/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E16" s="46">
+        <f>IFERROR(E33*(1-MIN(Assumptions!$C$6,30)/30)+D33*MIN(Assumptions!$C$6,30)/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="46">
+        <f>IFERROR(F33*(1-MIN(Assumptions!$C$6,30)/30)+E33*MIN(Assumptions!$C$6,30)/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="46">
+        <f>IFERROR(G33*(1-MIN(Assumptions!$C$6,30)/30)+F33*MIN(Assumptions!$C$6,30)/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="46">
+        <f>IFERROR(H33*(1-MIN(Assumptions!$C$6,30)/30)+G33*MIN(Assumptions!$C$6,30)/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="46">
+        <f>IFERROR(I33*(1-MIN(Assumptions!$C$6,30)/30)+H33*MIN(Assumptions!$C$6,30)/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="46">
+        <f>IFERROR(J33*(1-MIN(Assumptions!$C$6,30)/30)+I33*MIN(Assumptions!$C$6,30)/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="46">
+        <f>IFERROR(K33*(1-MIN(Assumptions!$C$6,30)/30)+J33*MIN(Assumptions!$C$6,30)/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="46">
+        <f>IFERROR(L33*(1-MIN(Assumptions!$C$6,30)/30)+K33*MIN(Assumptions!$C$6,30)/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M16" s="46">
+        <f>IFERROR(M33*(1-MIN(Assumptions!$C$6,30)/30)+L33*MIN(Assumptions!$C$6,30)/30,0)</f>
         <v>0.0</v>
       </c>
     </row>
@@ -2012,40 +2026,40 @@
           <t>Payroll (net pay)</t>
         </is>
       </c>
-      <c r="B17" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="43" t="n">
+      <c r="B17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2055,50 +2069,50 @@
           <t>Employer payroll taxes deposited (last month's)</t>
         </is>
       </c>
-      <c r="B18" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="45">
+      <c r="B18" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="46">
         <f>B34</f>
         <v>0.0</v>
       </c>
-      <c r="D18" s="45">
+      <c r="D18" s="46">
         <f>C34</f>
         <v>0.0</v>
       </c>
-      <c r="E18" s="45">
+      <c r="E18" s="46">
         <f>D34</f>
         <v>0.0</v>
       </c>
-      <c r="F18" s="45">
+      <c r="F18" s="46">
         <f>E34</f>
         <v>0.0</v>
       </c>
-      <c r="G18" s="45">
+      <c r="G18" s="46">
         <f>F34</f>
         <v>0.0</v>
       </c>
-      <c r="H18" s="45">
+      <c r="H18" s="46">
         <f>G34</f>
         <v>0.0</v>
       </c>
-      <c r="I18" s="45">
+      <c r="I18" s="46">
         <f>H34</f>
         <v>0.0</v>
       </c>
-      <c r="J18" s="45">
+      <c r="J18" s="46">
         <f>I34</f>
         <v>0.0</v>
       </c>
-      <c r="K18" s="45">
+      <c r="K18" s="46">
         <f>J34</f>
         <v>0.0</v>
       </c>
-      <c r="L18" s="45">
+      <c r="L18" s="46">
         <f>K34</f>
         <v>0.0</v>
       </c>
-      <c r="M18" s="45">
+      <c r="M18" s="46">
         <f>L34</f>
         <v>0.0</v>
       </c>
@@ -2109,40 +2123,40 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B19" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="43" t="n">
+      <c r="B19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2152,40 +2166,40 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B20" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="43" t="n">
+      <c r="B20" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2195,40 +2209,40 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B21" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="43" t="n">
+      <c r="B21" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2238,40 +2252,40 @@
           <t>Accounting / Admin</t>
         </is>
       </c>
-      <c r="B22" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="43" t="n">
+      <c r="B22" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2281,40 +2295,40 @@
           <t>Loan payment</t>
         </is>
       </c>
-      <c r="B23" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="43" t="n">
+      <c r="B23" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2324,40 +2338,40 @@
           <t>Employee taxes withheld, deposited (income tax + FICA)</t>
         </is>
       </c>
-      <c r="B24" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="43" t="n">
+      <c r="B24" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2367,50 +2381,50 @@
           <t>Sales tax / VAT payment (quarterly) · January = input (last Q4)</t>
         </is>
       </c>
-      <c r="B25" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="46">
+      <c r="B25" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="47">
         <f>""</f>
         <v/>
       </c>
-      <c r="D25" s="46">
+      <c r="D25" s="47">
         <f>""</f>
         <v/>
       </c>
-      <c r="E25" s="46">
+      <c r="E25" s="47">
         <f>MAX(0,SUM($B$36:$D$36)-SUM($B$37:$D$37))</f>
         <v>0.0</v>
       </c>
-      <c r="F25" s="46">
+      <c r="F25" s="47">
         <f>""</f>
         <v/>
       </c>
-      <c r="G25" s="46">
+      <c r="G25" s="47">
         <f>""</f>
         <v/>
       </c>
-      <c r="H25" s="46">
+      <c r="H25" s="47">
         <f>MAX(0,SUM($E$36:$G$36)-SUM($E$37:$G$37))</f>
         <v>0.0</v>
       </c>
-      <c r="I25" s="46">
+      <c r="I25" s="47">
         <f>""</f>
         <v/>
       </c>
-      <c r="J25" s="46">
+      <c r="J25" s="47">
         <f>""</f>
         <v/>
       </c>
-      <c r="K25" s="46">
+      <c r="K25" s="47">
         <f>MAX(0,SUM($H$36:$J$36)-SUM($H$37:$J$37))</f>
         <v>0.0</v>
       </c>
-      <c r="L25" s="46">
+      <c r="L25" s="47">
         <f>""</f>
         <v/>
       </c>
-      <c r="M25" s="46">
+      <c r="M25" s="47">
         <f>""</f>
         <v/>
       </c>
@@ -2421,40 +2435,40 @@
           <t>Delivery platform fees and other payments</t>
         </is>
       </c>
-      <c r="B26" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="43" t="n">
+      <c r="B26" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2464,51 +2478,51 @@
           <t>TOTAL PAYMENTS</t>
         </is>
       </c>
-      <c r="B27" s="44">
+      <c r="B27" s="45">
         <f>SUM(B16:B26)</f>
         <v>0.0</v>
       </c>
-      <c r="C27" s="44">
+      <c r="C27" s="45">
         <f>SUM(C16:C26)</f>
         <v>0.0</v>
       </c>
-      <c r="D27" s="44">
+      <c r="D27" s="45">
         <f>SUM(D16:D26)</f>
         <v>0.0</v>
       </c>
-      <c r="E27" s="44">
+      <c r="E27" s="45">
         <f>SUM(E16:E26)</f>
         <v>0.0</v>
       </c>
-      <c r="F27" s="44">
+      <c r="F27" s="45">
         <f>SUM(F16:F26)</f>
         <v>0.0</v>
       </c>
-      <c r="G27" s="44">
+      <c r="G27" s="45">
         <f>SUM(G16:G26)</f>
         <v>0.0</v>
       </c>
-      <c r="H27" s="44">
+      <c r="H27" s="45">
         <f>SUM(H16:H26)</f>
         <v>0.0</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="45">
         <f>SUM(I16:I26)</f>
         <v>0.0</v>
       </c>
-      <c r="J27" s="44">
+      <c r="J27" s="45">
         <f>SUM(J16:J26)</f>
         <v>0.0</v>
       </c>
-      <c r="K27" s="44">
+      <c r="K27" s="45">
         <f>SUM(K16:K26)</f>
         <v>0.0</v>
       </c>
-      <c r="L27" s="44">
+      <c r="L27" s="45">
         <f>SUM(L16:L26)</f>
         <v>0.0</v>
       </c>
-      <c r="M27" s="44">
+      <c r="M27" s="45">
         <f>SUM(M16:M26)</f>
         <v>0.0</v>
       </c>
@@ -2519,51 +2533,51 @@
           <t>NET CASH FLOW FOR THE MONTH</t>
         </is>
       </c>
-      <c r="B28" s="44">
+      <c r="B28" s="45">
         <f>B14-B27</f>
         <v>0.0</v>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="45">
         <f>C14-C27</f>
         <v>0.0</v>
       </c>
-      <c r="D28" s="44">
+      <c r="D28" s="45">
         <f>D14-D27</f>
         <v>0.0</v>
       </c>
-      <c r="E28" s="44">
+      <c r="E28" s="45">
         <f>E14-E27</f>
         <v>0.0</v>
       </c>
-      <c r="F28" s="44">
+      <c r="F28" s="45">
         <f>F14-F27</f>
         <v>0.0</v>
       </c>
-      <c r="G28" s="44">
+      <c r="G28" s="45">
         <f>G14-G27</f>
         <v>0.0</v>
       </c>
-      <c r="H28" s="44">
+      <c r="H28" s="45">
         <f>H14-H27</f>
         <v>0.0</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="45">
         <f>I14-I27</f>
         <v>0.0</v>
       </c>
-      <c r="J28" s="44">
+      <c r="J28" s="45">
         <f>J14-J27</f>
         <v>0.0</v>
       </c>
-      <c r="K28" s="44">
+      <c r="K28" s="45">
         <f>K14-K27</f>
         <v>0.0</v>
       </c>
-      <c r="L28" s="44">
+      <c r="L28" s="45">
         <f>L14-L27</f>
         <v>0.0</v>
       </c>
-      <c r="M28" s="44">
+      <c r="M28" s="45">
         <f>M14-M27</f>
         <v>0.0</v>
       </c>
@@ -2574,51 +2588,51 @@
           <t>ENDING BALANCE</t>
         </is>
       </c>
-      <c r="B29" s="44">
+      <c r="B29" s="45">
         <f>B5+B28</f>
         <v>15000.0</v>
       </c>
-      <c r="C29" s="44">
+      <c r="C29" s="45">
         <f>C5+C28</f>
         <v>15000.0</v>
       </c>
-      <c r="D29" s="44">
+      <c r="D29" s="45">
         <f>D5+D28</f>
         <v>15000.0</v>
       </c>
-      <c r="E29" s="44">
+      <c r="E29" s="45">
         <f>E5+E28</f>
         <v>15000.0</v>
       </c>
-      <c r="F29" s="44">
+      <c r="F29" s="45">
         <f>F5+F28</f>
         <v>15000.0</v>
       </c>
-      <c r="G29" s="44">
+      <c r="G29" s="45">
         <f>G5+G28</f>
         <v>15000.0</v>
       </c>
-      <c r="H29" s="44">
+      <c r="H29" s="45">
         <f>H5+H28</f>
         <v>15000.0</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="45">
         <f>I5+I28</f>
         <v>15000.0</v>
       </c>
-      <c r="J29" s="44">
+      <c r="J29" s="45">
         <f>J5+J28</f>
         <v>15000.0</v>
       </c>
-      <c r="K29" s="44">
+      <c r="K29" s="45">
         <f>K5+K28</f>
         <v>15000.0</v>
       </c>
-      <c r="L29" s="44">
+      <c r="L29" s="45">
         <f>L5+L28</f>
         <v>15000.0</v>
       </c>
-      <c r="M29" s="44">
+      <c r="M29" s="45">
         <f>M5+M28</f>
         <v>15000.0</v>
       </c>
@@ -2648,40 +2662,40 @@
           <t>Food purchases for the month (incl. sales tax)</t>
         </is>
       </c>
-      <c r="B33" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="43" t="n">
+      <c r="B33" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2691,95 +2705,95 @@
           <t>Employer payroll taxes accrued this month</t>
         </is>
       </c>
-      <c r="B34" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="43" t="n">
+      <c r="B34" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="44" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="37" t="inlineStr">
         <is>
-          <t>Sales tax / VAT collected this month</t>
-        </is>
-      </c>
-      <c r="B36" s="47">
-        <f>IFERROR(B12-B12/(1+Assumptions!$C$7),0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="C36" s="47">
-        <f>IFERROR(C12-C12/(1+Assumptions!$C$7),0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="D36" s="47">
-        <f>IFERROR(D12-D12/(1+Assumptions!$C$7),0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E36" s="47">
-        <f>IFERROR(E12-E12/(1+Assumptions!$C$7),0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="F36" s="47">
-        <f>IFERROR(F12-F12/(1+Assumptions!$C$7),0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="G36" s="47">
-        <f>IFERROR(G12-G12/(1+Assumptions!$C$7),0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="H36" s="47">
-        <f>IFERROR(H12-H12/(1+Assumptions!$C$7),0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="I36" s="47">
-        <f>IFERROR(I12-I12/(1+Assumptions!$C$7),0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="J36" s="47">
-        <f>IFERROR(J12-J12/(1+Assumptions!$C$7),0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="K36" s="47">
-        <f>IFERROR(K12-K12/(1+Assumptions!$C$7),0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="L36" s="47">
-        <f>IFERROR(L12-L12/(1+Assumptions!$C$7),0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="M36" s="47">
-        <f>IFERROR(M12-M12/(1+Assumptions!$C$7),0)</f>
+          <t>Sales tax / VAT collected this month (rows 7, 8 and 10)</t>
+        </is>
+      </c>
+      <c r="B36" s="48">
+        <f>IFERROR((B7+B8+B10)-(B7+B8+B10)/(1+Assumptions!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C36" s="48">
+        <f>IFERROR((C7+C8+C10)-(C7+C8+C10)/(1+Assumptions!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D36" s="48">
+        <f>IFERROR((D7+D8+D10)-(D7+D8+D10)/(1+Assumptions!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E36" s="48">
+        <f>IFERROR((E7+E8+E10)-(E7+E8+E10)/(1+Assumptions!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F36" s="48">
+        <f>IFERROR((F7+F8+F10)-(F7+F8+F10)/(1+Assumptions!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G36" s="48">
+        <f>IFERROR((G7+G8+G10)-(G7+G8+G10)/(1+Assumptions!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="H36" s="48">
+        <f>IFERROR((H7+H8+H10)-(H7+H8+H10)/(1+Assumptions!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I36" s="48">
+        <f>IFERROR((I7+I8+I10)-(I7+I8+I10)/(1+Assumptions!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="J36" s="48">
+        <f>IFERROR((J7+J8+J10)-(J7+J8+J10)/(1+Assumptions!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="K36" s="48">
+        <f>IFERROR((K7+K8+K10)-(K7+K8+K10)/(1+Assumptions!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="L36" s="48">
+        <f>IFERROR((L7+L8+L10)-(L7+L8+L10)/(1+Assumptions!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M36" s="48">
+        <f>IFERROR((M7+M8+M10)-(M7+M8+M10)/(1+Assumptions!$C$7),0)</f>
         <v>0.0</v>
       </c>
     </row>
@@ -2789,51 +2803,51 @@
           <t>Recoverable tax paid this month (UK VAT; US: 0)</t>
         </is>
       </c>
-      <c r="B37" s="47">
+      <c r="B37" s="48">
         <f>IFERROR(B33-B33/(1+Assumptions!$C$8)+(B19+B20+B21+B22)-(B19+B20+B21+B22)/(1+Assumptions!$C$9),0)</f>
         <v>0.0</v>
       </c>
-      <c r="C37" s="47">
+      <c r="C37" s="48">
         <f>IFERROR(C33-C33/(1+Assumptions!$C$8)+(C19+C20+C21+C22)-(C19+C20+C21+C22)/(1+Assumptions!$C$9),0)</f>
         <v>0.0</v>
       </c>
-      <c r="D37" s="47">
+      <c r="D37" s="48">
         <f>IFERROR(D33-D33/(1+Assumptions!$C$8)+(D19+D20+D21+D22)-(D19+D20+D21+D22)/(1+Assumptions!$C$9),0)</f>
         <v>0.0</v>
       </c>
-      <c r="E37" s="47">
+      <c r="E37" s="48">
         <f>IFERROR(E33-E33/(1+Assumptions!$C$8)+(E19+E20+E21+E22)-(E19+E20+E21+E22)/(1+Assumptions!$C$9),0)</f>
         <v>0.0</v>
       </c>
-      <c r="F37" s="47">
+      <c r="F37" s="48">
         <f>IFERROR(F33-F33/(1+Assumptions!$C$8)+(F19+F20+F21+F22)-(F19+F20+F21+F22)/(1+Assumptions!$C$9),0)</f>
         <v>0.0</v>
       </c>
-      <c r="G37" s="47">
+      <c r="G37" s="48">
         <f>IFERROR(G33-G33/(1+Assumptions!$C$8)+(G19+G20+G21+G22)-(G19+G20+G21+G22)/(1+Assumptions!$C$9),0)</f>
         <v>0.0</v>
       </c>
-      <c r="H37" s="47">
+      <c r="H37" s="48">
         <f>IFERROR(H33-H33/(1+Assumptions!$C$8)+(H19+H20+H21+H22)-(H19+H20+H21+H22)/(1+Assumptions!$C$9),0)</f>
         <v>0.0</v>
       </c>
-      <c r="I37" s="47">
+      <c r="I37" s="48">
         <f>IFERROR(I33-I33/(1+Assumptions!$C$8)+(I19+I20+I21+I22)-(I19+I20+I21+I22)/(1+Assumptions!$C$9),0)</f>
         <v>0.0</v>
       </c>
-      <c r="J37" s="47">
+      <c r="J37" s="48">
         <f>IFERROR(J33-J33/(1+Assumptions!$C$8)+(J19+J20+J21+J22)-(J19+J20+J21+J22)/(1+Assumptions!$C$9),0)</f>
         <v>0.0</v>
       </c>
-      <c r="K37" s="47">
+      <c r="K37" s="48">
         <f>IFERROR(K33-K33/(1+Assumptions!$C$8)+(K19+K20+K21+K22)-(K19+K20+K21+K22)/(1+Assumptions!$C$9),0)</f>
         <v>0.0</v>
       </c>
-      <c r="L37" s="47">
+      <c r="L37" s="48">
         <f>IFERROR(L33-L33/(1+Assumptions!$C$8)+(L19+L20+L21+L22)-(L19+L20+L21+L22)/(1+Assumptions!$C$9),0)</f>
         <v>0.0</v>
       </c>
-      <c r="M37" s="47">
+      <c r="M37" s="48">
         <f>IFERROR(M33-M33/(1+Assumptions!$C$8)+(M19+M20+M21+M22)-(M19+M20+M21+M22)/(1+Assumptions!$C$9),0)</f>
         <v>0.0</v>
       </c>
@@ -2844,51 +2858,51 @@
           <t>Suggested sales by seasonality (for reference)</t>
         </is>
       </c>
-      <c r="B39" s="47">
+      <c r="B39" s="48">
         <f>Assumptions!$D$13</f>
         <v>0.0</v>
       </c>
-      <c r="C39" s="47">
+      <c r="C39" s="48">
         <f>Assumptions!$D$14</f>
         <v>0.0</v>
       </c>
-      <c r="D39" s="47">
+      <c r="D39" s="48">
         <f>Assumptions!$D$15</f>
         <v>0.0</v>
       </c>
-      <c r="E39" s="47">
+      <c r="E39" s="48">
         <f>Assumptions!$D$16</f>
         <v>0.0</v>
       </c>
-      <c r="F39" s="47">
+      <c r="F39" s="48">
         <f>Assumptions!$D$17</f>
         <v>0.0</v>
       </c>
-      <c r="G39" s="47">
+      <c r="G39" s="48">
         <f>Assumptions!$D$18</f>
         <v>0.0</v>
       </c>
-      <c r="H39" s="47">
+      <c r="H39" s="48">
         <f>Assumptions!$D$19</f>
         <v>0.0</v>
       </c>
-      <c r="I39" s="47">
+      <c r="I39" s="48">
         <f>Assumptions!$D$20</f>
         <v>0.0</v>
       </c>
-      <c r="J39" s="47">
+      <c r="J39" s="48">
         <f>Assumptions!$D$21</f>
         <v>0.0</v>
       </c>
-      <c r="K39" s="47">
+      <c r="K39" s="48">
         <f>Assumptions!$D$22</f>
         <v>0.0</v>
       </c>
-      <c r="L39" s="47">
+      <c r="L39" s="48">
         <f>Assumptions!$D$23</f>
         <v>0.0</v>
       </c>
-      <c r="M39" s="47">
+      <c r="M39" s="48">
         <f>Assumptions!$D$24</f>
         <v>0.0</v>
       </c>
@@ -2958,7 +2972,7 @@
           <t>Safety threshold:</t>
         </is>
       </c>
-      <c r="C3" s="48" t="n">
+      <c r="C3" s="49" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -2991,7 +3005,7 @@
           <t>Jan</t>
         </is>
       </c>
-      <c r="C6" s="45">
+      <c r="C6" s="46">
         <f>'Monthly Cash Flow'!B29</f>
         <v>15000.0</v>
       </c>
@@ -2999,7 +3013,7 @@
         <f>IF('Monthly Cash Flow'!B12+'Monthly Cash Flow'!B27=0,"—",IF(C6&lt;$C$3,"⚠️ BELOW MINIMUM","OK"))</f>
         <v>—</v>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="42">
         <f>$C$3</f>
         <v>5000.0</v>
       </c>
@@ -3010,7 +3024,7 @@
           <t>Feb</t>
         </is>
       </c>
-      <c r="C7" s="45">
+      <c r="C7" s="46">
         <f>'Monthly Cash Flow'!C29</f>
         <v>15000.0</v>
       </c>
@@ -3018,7 +3032,7 @@
         <f>IF('Monthly Cash Flow'!C12+'Monthly Cash Flow'!C27=0,"—",IF(C7&lt;$C$3,"⚠️ BELOW MINIMUM","OK"))</f>
         <v>—</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="42">
         <f>$C$3</f>
         <v>5000.0</v>
       </c>
@@ -3029,7 +3043,7 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="C8" s="45">
+      <c r="C8" s="46">
         <f>'Monthly Cash Flow'!D29</f>
         <v>15000.0</v>
       </c>
@@ -3037,7 +3051,7 @@
         <f>IF('Monthly Cash Flow'!D12+'Monthly Cash Flow'!D27=0,"—",IF(C8&lt;$C$3,"⚠️ BELOW MINIMUM","OK"))</f>
         <v>—</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="42">
         <f>$C$3</f>
         <v>5000.0</v>
       </c>
@@ -3048,7 +3062,7 @@
           <t>Apr</t>
         </is>
       </c>
-      <c r="C9" s="45">
+      <c r="C9" s="46">
         <f>'Monthly Cash Flow'!E29</f>
         <v>15000.0</v>
       </c>
@@ -3056,7 +3070,7 @@
         <f>IF('Monthly Cash Flow'!E12+'Monthly Cash Flow'!E27=0,"—",IF(C9&lt;$C$3,"⚠️ BELOW MINIMUM","OK"))</f>
         <v>—</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="42">
         <f>$C$3</f>
         <v>5000.0</v>
       </c>
@@ -3067,7 +3081,7 @@
           <t>May</t>
         </is>
       </c>
-      <c r="C10" s="45">
+      <c r="C10" s="46">
         <f>'Monthly Cash Flow'!F29</f>
         <v>15000.0</v>
       </c>
@@ -3075,7 +3089,7 @@
         <f>IF('Monthly Cash Flow'!F12+'Monthly Cash Flow'!F27=0,"—",IF(C10&lt;$C$3,"⚠️ BELOW MINIMUM","OK"))</f>
         <v>—</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="42">
         <f>$C$3</f>
         <v>5000.0</v>
       </c>
@@ -3086,7 +3100,7 @@
           <t>Jun</t>
         </is>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="46">
         <f>'Monthly Cash Flow'!G29</f>
         <v>15000.0</v>
       </c>
@@ -3094,7 +3108,7 @@
         <f>IF('Monthly Cash Flow'!G12+'Monthly Cash Flow'!G27=0,"—",IF(C11&lt;$C$3,"⚠️ BELOW MINIMUM","OK"))</f>
         <v>—</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="42">
         <f>$C$3</f>
         <v>5000.0</v>
       </c>
@@ -3105,7 +3119,7 @@
           <t>Jul</t>
         </is>
       </c>
-      <c r="C12" s="45">
+      <c r="C12" s="46">
         <f>'Monthly Cash Flow'!H29</f>
         <v>15000.0</v>
       </c>
@@ -3113,7 +3127,7 @@
         <f>IF('Monthly Cash Flow'!H12+'Monthly Cash Flow'!H27=0,"—",IF(C12&lt;$C$3,"⚠️ BELOW MINIMUM","OK"))</f>
         <v>—</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="42">
         <f>$C$3</f>
         <v>5000.0</v>
       </c>
@@ -3124,7 +3138,7 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="C13" s="45">
+      <c r="C13" s="46">
         <f>'Monthly Cash Flow'!I29</f>
         <v>15000.0</v>
       </c>
@@ -3132,7 +3146,7 @@
         <f>IF('Monthly Cash Flow'!I12+'Monthly Cash Flow'!I27=0,"—",IF(C13&lt;$C$3,"⚠️ BELOW MINIMUM","OK"))</f>
         <v>—</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="42">
         <f>$C$3</f>
         <v>5000.0</v>
       </c>
@@ -3143,7 +3157,7 @@
           <t>Sep</t>
         </is>
       </c>
-      <c r="C14" s="45">
+      <c r="C14" s="46">
         <f>'Monthly Cash Flow'!J29</f>
         <v>15000.0</v>
       </c>
@@ -3151,7 +3165,7 @@
         <f>IF('Monthly Cash Flow'!J12+'Monthly Cash Flow'!J27=0,"—",IF(C14&lt;$C$3,"⚠️ BELOW MINIMUM","OK"))</f>
         <v>—</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="42">
         <f>$C$3</f>
         <v>5000.0</v>
       </c>
@@ -3162,7 +3176,7 @@
           <t>Oct</t>
         </is>
       </c>
-      <c r="C15" s="45">
+      <c r="C15" s="46">
         <f>'Monthly Cash Flow'!K29</f>
         <v>15000.0</v>
       </c>
@@ -3170,7 +3184,7 @@
         <f>IF('Monthly Cash Flow'!K12+'Monthly Cash Flow'!K27=0,"—",IF(C15&lt;$C$3,"⚠️ BELOW MINIMUM","OK"))</f>
         <v>—</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="42">
         <f>$C$3</f>
         <v>5000.0</v>
       </c>
@@ -3181,7 +3195,7 @@
           <t>Nov</t>
         </is>
       </c>
-      <c r="C16" s="45">
+      <c r="C16" s="46">
         <f>'Monthly Cash Flow'!L29</f>
         <v>15000.0</v>
       </c>
@@ -3189,7 +3203,7 @@
         <f>IF('Monthly Cash Flow'!L12+'Monthly Cash Flow'!L27=0,"—",IF(C16&lt;$C$3,"⚠️ BELOW MINIMUM","OK"))</f>
         <v>—</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="42">
         <f>$C$3</f>
         <v>5000.0</v>
       </c>
@@ -3200,7 +3214,7 @@
           <t>Dec</t>
         </is>
       </c>
-      <c r="C17" s="45">
+      <c r="C17" s="46">
         <f>'Monthly Cash Flow'!M29</f>
         <v>15000.0</v>
       </c>
@@ -3208,7 +3222,7 @@
         <f>IF('Monthly Cash Flow'!M12+'Monthly Cash Flow'!M27=0,"—",IF(C17&lt;$C$3,"⚠️ BELOW MINIMUM","OK"))</f>
         <v>—</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="42">
         <f>$C$3</f>
         <v>5000.0</v>
       </c>
